--- a/Generators/Experiment with utility data leak/utility results/10. Metro interstate/TRTR_TSTR_results_merged.xlsx
+++ b/Generators/Experiment with utility data leak/utility results/10. Metro interstate/TRTR_TSTR_results_merged.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quality_Metrics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TRTR_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="All_Comparisons" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CTGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CopulaGAN" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TVAE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GaussianCopula" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="WGAN_GP" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CTABGAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WGAN_GP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTABGAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,13 +28,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +56,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,21 +436,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Quality_Score</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -527,6 +541,36 @@
         <v>0.672640394441528</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9053272950819673</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8240340163934425</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
@@ -547,152 +591,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -1815,6 +1859,2578 @@
       <c r="AD11" t="inlineStr">
         <is>
           <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_Increase</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Increase</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Increase</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.02197954877106871</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0931319739814164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4190833.005087733</v>
+      </c>
+      <c r="E2" t="n">
+        <v>338025.6045214536</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2045.723106278084</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80.62242263014029</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1765.52881925974</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49.61090621555741</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0931</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4190833.0051 ± 338025.6045</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2045.7231 ± 80.6224</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1765.5288 ± 49.6109</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.7178776544069405</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1893777979633678</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7148589.705998076</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>652247.6626055934</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2671.132442621315</v>
+      </c>
+      <c r="S2" t="n">
+        <v>123.1132269000258</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2269.577435433921</v>
+      </c>
+      <c r="U2" t="n">
+        <v>99.07151751254837</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-0.7179 ± 0.1894</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>7148589.7060 ± 652247.6626</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2671.1324 ± 123.1132</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2269.5774 ± 99.0715</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.6958981056358718</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2957756.700910343</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>625.4093363432307</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>504.048616174181</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.02202379141697535</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09327798340599044</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4191008.940626054</v>
+      </c>
+      <c r="E3" t="n">
+        <v>338623.7087407181</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2045.761228163767</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80.75984953985314</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1765.456276809517</v>
+      </c>
+      <c r="I3" t="n">
+        <v>49.70998560185271</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0933</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4191008.9406 ± 338623.7087</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2045.7612 ± 80.7598</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1765.4563 ± 49.7100</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.7188787044824536</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1899670471610221</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7152739.786272645</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>654933.5699019413</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2671.889546796317</v>
+      </c>
+      <c r="S3" t="n">
+        <v>123.5854899484475</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2270.111429777064</v>
+      </c>
+      <c r="U3" t="n">
+        <v>99.38176451673746</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-0.7189 ± 0.1900</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7152739.7863 ± 654933.5699</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2671.8895 ± 123.5855</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2270.1114 ± 99.3818</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.6968549130654783</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2961730.845646591</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>626.12831863255</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>504.6551529675469</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.02204459551775029</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09337855142992794</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4191091.420878544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>339054.5694780927</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2045.777829721612</v>
+      </c>
+      <c r="G4" t="n">
+        <v>80.85990833311384</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1765.393478151547</v>
+      </c>
+      <c r="I4" t="n">
+        <v>49.77236918291081</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0934</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4191091.4209 ± 339054.5695</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2045.7778 ± 80.8599</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1765.3935 ± 49.7724</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.7198892142587445</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1905674410824654</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7156929.271749449</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>657674.2476710969</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2672.653328403318</v>
+      </c>
+      <c r="S4" t="n">
+        <v>124.0674454754247</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2270.64908160909</v>
+      </c>
+      <c r="U4" t="n">
+        <v>99.69313836738019</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-0.7199 ± 0.1906</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7156929.2717 ± 657674.2477</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2672.6533 ± 124.0674</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2270.6491 ± 99.6931</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.6978446187409942</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2965837.850870905</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>626.8754986817053</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>505.2556034575427</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.02363182357272349</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09562120929438869</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4197301.361197427</v>
+      </c>
+      <c r="E5" t="n">
+        <v>344679.8161882583</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2047.246722126397</v>
+      </c>
+      <c r="G5" t="n">
+        <v>82.20719041373771</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1766.71915181769</v>
+      </c>
+      <c r="I5" t="n">
+        <v>51.57481027024704</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.0236 ± 0.0956</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4197301.3612 ± 344679.8162</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2047.2467 ± 82.2072</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1766.7192 ± 51.5748</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.719883683299112</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1905641845641041</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7156906.294132091</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>657659.5462738692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2672.649138326419</v>
+      </c>
+      <c r="S5" t="n">
+        <v>124.064846552732</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2270.645819513629</v>
+      </c>
+      <c r="U5" t="n">
+        <v>99.69124765822308</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-0.7199 ± 0.1906</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>7156906.2941 ± 657659.5463</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2672.6491 ± 124.0648</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2270.6458 ± 99.6912</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.6962518597263885</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2959604.932934664</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>625.4024162000221</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>503.9266676959392</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.0293523377117139</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.07005792052475614</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4222447.845562431</v>
+      </c>
+      <c r="E6" t="n">
+        <v>248994.8517990398</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2054.051195245206</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60.75024347616055</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1794.716049097572</v>
+      </c>
+      <c r="I6" t="n">
+        <v>61.22856451392724</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.0294 ± 0.0701</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4222447.8456 ± 248994.8518</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2054.0512 ± 60.7502</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1794.7160 ± 61.2286</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1263738429704712</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1222145558875543</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4687055.047805268</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>418304.8650110241</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2162.96095327205</v>
+      </c>
+      <c r="S6" t="n">
+        <v>98.06439168976064</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1823.828835653621</v>
+      </c>
+      <c r="U6" t="n">
+        <v>83.11285297640444</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-0.1264 ± 0.1222</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4687055.0478 ± 418304.8650</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2162.9610 ± 98.0644</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1823.8288 ± 83.1129</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.09702150525875733</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>464607.2022428373</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>108.909758026844</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>29.1127865560486</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.04522384586573791</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.02969755150601561</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4292253.001770332</v>
+      </c>
+      <c r="E7" t="n">
+        <v>201312.7535934005</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2071.259558225389</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.72649553372899</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1855.681256810133</v>
+      </c>
+      <c r="I7" t="n">
+        <v>44.48179755879956</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.0452 ± 0.0297</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4292253.0018 ± 201312.7536</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2071.2596 ± 48.7265</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1855.6813 ± 44.4818</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.585111722634477</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.243080905082388</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10768783.02524476</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>929400.144337276</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3278.85279159589</v>
+      </c>
+      <c r="S7" t="n">
+        <v>141.0571054124456</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2570.118143764929</v>
+      </c>
+      <c r="U7" t="n">
+        <v>172.8449954986473</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-1.5851 ± 0.2431</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>10768783.0252 ± 929400.1443</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3278.8528 ± 141.0571</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2570.1181 ± 172.8450</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.539887876768739</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6476530.02347443</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1207.593233370501</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>714.4368869547955</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.2674879048880762</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1102508098838784</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5199525.514479999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>418987.0960349165</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2278.580226524359</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.87954537329404</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1930.904</v>
+      </c>
+      <c r="I8" t="n">
+        <v>87.79568920700689</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.2675 ± 0.1103</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5199525.5145 ± 418987.0960</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2278.5802 ± 91.8795</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1930.9040 ± 87.7957</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.50940040613677</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2414342496387683</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6260363.105479041</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>802186.6644520612</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2497.471121501854</v>
+      </c>
+      <c r="S8" t="n">
+        <v>159.8648830290949</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2070.284763137528</v>
+      </c>
+      <c r="U8" t="n">
+        <v>120.6611038599134</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-0.5094 ± 0.2414</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6260363.1055 ± 802186.6645</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2497.4711 ± 159.8649</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2070.2848 ± 120.6611</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2419125012486938</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1060837.590999042</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>218.890894977495</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>139.3807631375284</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.3360615620073734</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1378329076011162</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5484008.168167765</v>
+      </c>
+      <c r="E9" t="n">
+        <v>576403.3611653862</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2338.817409203663</v>
+      </c>
+      <c r="G9" t="n">
+        <v>124.4601434356985</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1976.35174841514</v>
+      </c>
+      <c r="I9" t="n">
+        <v>123.2861301883126</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.3361 ± 0.1378</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5484008.1682 ± 576403.3612</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2338.8174 ± 124.4601</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1976.3517 ± 123.2861</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.3080616474086598</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1667474238286133</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5456958.83693452</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>759922.2469249581</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2331.350182220014</v>
+      </c>
+      <c r="S9" t="n">
+        <v>155.5105026722121</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1935.390040832001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>129.4926922363996</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-0.3081 ± 0.1667</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5456958.8369 ± 759922.2469</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2331.3502 ± 155.5105</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1935.3900 ± 129.4927</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.02799991459871354</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-27049.33123324532</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-7.467226983648743</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-40.96170758313906</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.5095897393811551</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1766848228829434</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6200940.965746299</v>
+      </c>
+      <c r="E10" t="n">
+        <v>777167.7922437319</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2485.674362162478</v>
+      </c>
+      <c r="G10" t="n">
+        <v>157.6350603784267</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2051.180442857143</v>
+      </c>
+      <c r="I10" t="n">
+        <v>176.3899995810382</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.5096 ± 0.1767</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6200940.9657 ± 777167.7922</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2485.6744 ± 157.6351</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2051.1804 ± 176.3900</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.5881716273962396</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2620870858654061</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6617697.375980625</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1078627.281843615</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2565.256039968876</v>
+      </c>
+      <c r="S10" t="n">
+        <v>203.1934638707781</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2094.319049790908</v>
+      </c>
+      <c r="U10" t="n">
+        <v>146.7954427364796</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-0.5882 ± 0.2621</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6617697.3760 ± 1078627.2818</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2565.2560 ± 203.1935</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2094.3190 ± 146.7954</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.07858188801508448</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>416756.4102343256</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>79.5816778063986</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>43.138606933765</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.9240200916636427</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2197289926805912</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7901767.635233889</v>
+      </c>
+      <c r="E11" t="n">
+        <v>957048.788964997</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2806.02004944254</v>
+      </c>
+      <c r="G11" t="n">
+        <v>176.4436244885071</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2255.210983333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>191.7409568707387</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-0.9240 ± 0.2197</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7901767.6352 ± 957048.7890</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2806.0200 ± 176.4436</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2255.2110 ± 191.7410</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.9207057293678036</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1346455940171846</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8009991.033006666</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>616382.3816635744</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2828.259395841021</v>
+      </c>
+      <c r="S11" t="n">
+        <v>110.2513433712303</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2273.132322548322</v>
+      </c>
+      <c r="U11" t="n">
+        <v>88.63222868320217</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-0.9207 ± 0.1346</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>8009991.0330 ± 616382.3817</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2828.2594 ± 110.2513</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2273.1323 ± 88.6322</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.003314362295839146</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>108223.3977727769</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>22.2393463984813</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>17.92133921498862</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_Increase</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Increase</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Increase</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.02197954877106871</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0931319739814164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4190833.005087733</v>
+      </c>
+      <c r="E2" t="n">
+        <v>338025.6045214536</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2045.723106278084</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80.62242263014029</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1765.52881925974</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49.61090621555741</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0931</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4190833.0051 ± 338025.6045</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2045.7231 ± 80.6224</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1765.5288 ± 49.6109</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.006455780373212139</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04892348421770575</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4146450.483429372</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>304542.6127401009</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2035.049048973221</v>
+      </c>
+      <c r="S2" t="n">
+        <v>74.72803804136105</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1813.932735973819</v>
+      </c>
+      <c r="U2" t="n">
+        <v>87.40337371545974</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.0065 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4146450.4834 ± 304542.6127</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2035.0490 ± 74.7280</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>1813.9327 ± 87.4034</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.02843532914428085</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-44382.52165836096</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-10.67405730486348</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>48.40391671407929</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.02202379141697535</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09327798340599044</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4191008.940626054</v>
+      </c>
+      <c r="E3" t="n">
+        <v>338623.7087407181</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2045.761228163767</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80.75984953985314</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1765.456276809517</v>
+      </c>
+      <c r="I3" t="n">
+        <v>49.70998560185271</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0933</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4191008.9406 ± 338623.7087</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2045.7612 ± 80.7598</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1765.4563 ± 49.7100</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.006443161190610436</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04891651581300863</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4146501.173366891</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>304493.1542510501</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2035.061920175357</v>
+      </c>
+      <c r="S3" t="n">
+        <v>74.71541874993835</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1813.923255921103</v>
+      </c>
+      <c r="U3" t="n">
+        <v>87.38937488179191</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.0064 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4146501.1734 ± 304493.1543</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2035.0619 ± 74.7154</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1813.9233 ± 87.3894</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.02846695260758578</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-44507.76725916285</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-10.69930798840983</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>48.46697911158526</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.02204459551775029</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09337855142992794</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4191091.420878544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>339054.5694780927</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2045.777829721612</v>
+      </c>
+      <c r="G4" t="n">
+        <v>80.85990833311384</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1765.393478151547</v>
+      </c>
+      <c r="I4" t="n">
+        <v>49.77236918291081</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0934</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4191091.4209 ± 339054.5695</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2045.7778 ± 80.8599</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1765.3935 ± 49.7724</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.006429976379896229</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04890982816024889</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4146554.12791614</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>304442.9847094165</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2035.075353304413</v>
+      </c>
+      <c r="S4" t="n">
+        <v>74.70262741964505</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1813.913614388983</v>
+      </c>
+      <c r="U4" t="n">
+        <v>87.37513500768613</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.0064 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4146554.1279 ± 304442.9847</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2035.0754 ± 74.7026</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1813.9136 ± 87.3751</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.02847457189764652</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-44537.2929624049</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-10.70247641719948</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>48.52013623743619</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.02363182357272349</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09562120929438869</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4197301.361197427</v>
+      </c>
+      <c r="E5" t="n">
+        <v>344679.8161882583</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2047.246722126397</v>
+      </c>
+      <c r="G5" t="n">
+        <v>82.20719041373771</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1766.71915181769</v>
+      </c>
+      <c r="I5" t="n">
+        <v>51.57481027024704</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.0236 ± 0.0956</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4197301.3612 ± 344679.8162</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2047.2467 ± 82.2072</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1766.7192 ± 51.5748</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.006430457294040182</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04890951231155721</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4146552.212226189</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>304443.5292816404</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2035.074878444234</v>
+      </c>
+      <c r="S5" t="n">
+        <v>74.7027543101815</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1813.913792849644</v>
+      </c>
+      <c r="U5" t="n">
+        <v>87.375358114875</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.0064 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4146552.2122 ± 304443.5293</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2035.0749 ± 74.7028</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1813.9138 ± 87.3754</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.03006228086676367</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-50749.14897123817</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-12.17184368216294</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>47.19464103195423</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.0293523377117139</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.07005792052475614</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4222447.845562431</v>
+      </c>
+      <c r="E6" t="n">
+        <v>248994.8517990398</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2054.051195245206</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60.75024347616055</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1794.716049097572</v>
+      </c>
+      <c r="I6" t="n">
+        <v>61.22856451392724</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.0294 ± 0.0701</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4222447.8456 ± 248994.8518</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2054.0512 ± 60.7502</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1794.7160 ± 61.2286</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1298772540833849</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1200854675069694</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4710666.868215402</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>519132.5854161489</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2167.58008441026</v>
+      </c>
+      <c r="S6" t="n">
+        <v>116.7306771228909</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1907.240855702832</v>
+      </c>
+      <c r="U6" t="n">
+        <v>97.28380297497954</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-0.1299 ± 0.1201</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4710666.8682 ± 519132.5854</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2167.5801 ± 116.7307</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1907.2409 ± 97.2838</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.100524916371671</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>488219.0226529706</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>113.5288891650534</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>112.5248066052598</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.04522384586573791</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.02969755150601561</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4292253.001770332</v>
+      </c>
+      <c r="E7" t="n">
+        <v>201312.7535934005</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2071.259558225389</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.72649553372899</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1855.681256810133</v>
+      </c>
+      <c r="I7" t="n">
+        <v>44.48179755879956</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.0452 ± 0.0297</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4292253.0018 ± 201312.7536</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2071.2596 ± 48.7265</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1855.6813 ± 44.4818</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.119444220475687</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05477205586251412</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4673397.506005201</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>365366.9215896982</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2160.340664448072</v>
+      </c>
+      <c r="S7" t="n">
+        <v>83.83661052084295</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1913.191224798294</v>
+      </c>
+      <c r="U7" t="n">
+        <v>96.81010927698871</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-0.1194 ± 0.0548</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4673397.5060 ± 365366.9216</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2160.3407 ± 83.8366</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1913.1912 ± 96.8101</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.07422037460994904</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>381144.50423487</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>89.0811062226835</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>57.5099679881605</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.2674879048880762</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1102508098838784</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5199525.514479999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>418987.0960349165</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2278.580226524359</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.87954537329404</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1930.904</v>
+      </c>
+      <c r="I8" t="n">
+        <v>87.79568920700689</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.2675 ± 0.1103</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5199525.5145 ± 418987.0960</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2278.5802 ± 91.8795</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1930.9040 ± 87.7957</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.2011300080016346</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06946578729563883</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5009603.737679501</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>344676.7245957914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2237.038946505775</v>
+      </c>
+      <c r="S8" t="n">
+        <v>76.45252336386987</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1921.600020176245</v>
+      </c>
+      <c r="U8" t="n">
+        <v>75.18441880341632</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-0.2011 ± 0.0695</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>5009603.7377 ± 344676.7246</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2237.0389 ± 76.4525</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1921.6000 ± 75.1844</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.06635789688644153</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-189921.7768004984</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-41.54128001858362</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-9.303979823755071</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.3360615620073734</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1378329076011162</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5484008.168167765</v>
+      </c>
+      <c r="E9" t="n">
+        <v>576403.3611653862</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2338.817409203663</v>
+      </c>
+      <c r="G9" t="n">
+        <v>124.4601434356985</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1976.35174841514</v>
+      </c>
+      <c r="I9" t="n">
+        <v>123.2861301883126</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.3361 ± 0.1378</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5484008.1682 ± 576403.3612</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2338.8174 ± 124.4601</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1976.3517 ± 123.2861</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.1921497592830952</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1004141674748086</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4977471.6047949</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>526704.1128716948</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2228.375819521219</v>
+      </c>
+      <c r="S9" t="n">
+        <v>114.5659042164179</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1936.371111109163</v>
+      </c>
+      <c r="U9" t="n">
+        <v>104.3496113886036</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-0.1921 ± 0.1004</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4977471.6048 ± 526704.1129</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2228.3758 ± 114.5659</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1936.3711 ± 104.3496</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.1439118027242782</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-506536.5633728653</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-110.4415896824435</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-39.98063730597733</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.5095897393811551</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1766848228829434</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6200940.965746299</v>
+      </c>
+      <c r="E10" t="n">
+        <v>777167.7922437319</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2485.674362162478</v>
+      </c>
+      <c r="G10" t="n">
+        <v>157.6350603784267</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2051.180442857143</v>
+      </c>
+      <c r="I10" t="n">
+        <v>176.3899995810382</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.5096 ± 0.1767</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6200940.9657 ± 777167.7922</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2485.6744 ± 157.6351</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2051.1804 ± 176.3900</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.2198215910135217</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.07989282539604484</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5093951.67033181</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>471205.5773051113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2254.858646985713</v>
+      </c>
+      <c r="S10" t="n">
+        <v>103.0865464094777</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1939.822805199898</v>
+      </c>
+      <c r="U10" t="n">
+        <v>91.86529787293772</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-0.2198 ± 0.0799</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5093951.6703 ± 471205.5773</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2254.8586 ± 103.0865</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1939.8228 ± 91.8653</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.2897681483676334</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1106989.29541449</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-230.815715176765</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-111.3576376572446</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.9240200916636427</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2197289926805912</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7901767.635233889</v>
+      </c>
+      <c r="E11" t="n">
+        <v>957048.788964997</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2806.02004944254</v>
+      </c>
+      <c r="G11" t="n">
+        <v>176.4436244885071</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2255.210983333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>191.7409568707387</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-0.9240 ± 0.2197</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7901767.6352 ± 957048.7890</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2806.0200 ± 176.4436</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2255.2110 ± 191.7410</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.7328266672368908</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1755664423745648</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7224309.491849869</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>769090.78526603</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2684.481332654806</v>
+      </c>
+      <c r="S11" t="n">
+        <v>140.9076390869193</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2209.68196979916</v>
+      </c>
+      <c r="U11" t="n">
+        <v>124.9356439375182</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-0.7328 ± 0.1756</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>7224309.4918 ± 769090.7853</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2684.4813 ± 140.9076</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2209.6820 ± 124.9356</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.1911934244267519</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-677458.1433840198</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-121.5387167877334</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-45.52901353417337</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -1833,67 +4449,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)</t>
         </is>
@@ -2420,156 +5036,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -9292,6 +11908,2246 @@
       <c r="AD61" t="inlineStr">
         <is>
           <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.02197954877106871</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.0931319739814164</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4190833.005087733</v>
+      </c>
+      <c r="E62" t="n">
+        <v>338025.6045214536</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2045.723106278084</v>
+      </c>
+      <c r="G62" t="n">
+        <v>80.62242263014029</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1765.52881925974</v>
+      </c>
+      <c r="I62" t="n">
+        <v>49.61090621555741</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0931</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>4190833.0051 ± 338025.6045</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2045.7231 ± 80.6224</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1765.5288 ± 49.6109</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>-0.7178776544069405</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.1893777979633678</v>
+      </c>
+      <c r="P62" t="n">
+        <v>7148589.705998076</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>652247.6626055934</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2671.132442621315</v>
+      </c>
+      <c r="S62" t="n">
+        <v>123.1132269000258</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2269.577435433921</v>
+      </c>
+      <c r="U62" t="n">
+        <v>99.07151751254837</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>-0.7179 ± 0.1894</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>7148589.7060 ± 652247.6626</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>2671.1324 ± 123.1132</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2269.5774 ± 99.0715</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.6958981056358718</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>2957756.700910343</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>625.4093363432307</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>504.048616174181</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-0.02202379141697535</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.09327798340599044</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4191008.940626054</v>
+      </c>
+      <c r="E63" t="n">
+        <v>338623.7087407181</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2045.761228163767</v>
+      </c>
+      <c r="G63" t="n">
+        <v>80.75984953985314</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1765.456276809517</v>
+      </c>
+      <c r="I63" t="n">
+        <v>49.70998560185271</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0933</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>4191008.9406 ± 338623.7087</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2045.7612 ± 80.7598</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1765.4563 ± 49.7100</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>-0.7188787044824536</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.1899670471610221</v>
+      </c>
+      <c r="P63" t="n">
+        <v>7152739.786272645</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>654933.5699019413</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2671.889546796317</v>
+      </c>
+      <c r="S63" t="n">
+        <v>123.5854899484475</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2270.111429777064</v>
+      </c>
+      <c r="U63" t="n">
+        <v>99.38176451673746</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>-0.7189 ± 0.1900</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>7152739.7863 ± 654933.5699</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>2671.8895 ± 123.5855</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2270.1114 ± 99.3818</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.6968549130654783</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2961730.845646591</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>626.12831863255</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>504.6551529675469</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.02204459551775029</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.09337855142992794</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4191091.420878544</v>
+      </c>
+      <c r="E64" t="n">
+        <v>339054.5694780927</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2045.777829721612</v>
+      </c>
+      <c r="G64" t="n">
+        <v>80.85990833311384</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1765.393478151547</v>
+      </c>
+      <c r="I64" t="n">
+        <v>49.77236918291081</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0934</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>4191091.4209 ± 339054.5695</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2045.7778 ± 80.8599</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1765.3935 ± 49.7724</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>-0.7198892142587445</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.1905674410824654</v>
+      </c>
+      <c r="P64" t="n">
+        <v>7156929.271749449</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>657674.2476710969</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2672.653328403318</v>
+      </c>
+      <c r="S64" t="n">
+        <v>124.0674454754247</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2270.64908160909</v>
+      </c>
+      <c r="U64" t="n">
+        <v>99.69313836738019</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>-0.7199 ± 0.1906</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>7156929.2717 ± 657674.2477</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>2672.6533 ± 124.0674</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2270.6491 ± 99.6931</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.6978446187409942</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2965837.850870905</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>626.8754986817053</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>505.2556034575427</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.02363182357272349</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.09562120929438869</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4197301.361197427</v>
+      </c>
+      <c r="E65" t="n">
+        <v>344679.8161882583</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2047.246722126397</v>
+      </c>
+      <c r="G65" t="n">
+        <v>82.20719041373771</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1766.71915181769</v>
+      </c>
+      <c r="I65" t="n">
+        <v>51.57481027024704</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>-0.0236 ± 0.0956</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>4197301.3612 ± 344679.8162</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2047.2467 ± 82.2072</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1766.7192 ± 51.5748</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>-0.719883683299112</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.1905641845641041</v>
+      </c>
+      <c r="P65" t="n">
+        <v>7156906.294132091</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>657659.5462738692</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2672.649138326419</v>
+      </c>
+      <c r="S65" t="n">
+        <v>124.064846552732</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2270.645819513629</v>
+      </c>
+      <c r="U65" t="n">
+        <v>99.69124765822308</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>-0.7199 ± 0.1906</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>7156906.2941 ± 657659.5463</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>2672.6491 ± 124.0648</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2270.6458 ± 99.6912</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.6962518597263885</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>2959604.932934664</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>625.4024162000221</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>503.9266676959392</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.0293523377117139</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.07005792052475614</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4222447.845562431</v>
+      </c>
+      <c r="E66" t="n">
+        <v>248994.8517990398</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2054.051195245206</v>
+      </c>
+      <c r="G66" t="n">
+        <v>60.75024347616055</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1794.716049097572</v>
+      </c>
+      <c r="I66" t="n">
+        <v>61.22856451392724</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-0.0294 ± 0.0701</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>4222447.8456 ± 248994.8518</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2054.0512 ± 60.7502</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1794.7160 ± 61.2286</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>-0.1263738429704712</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.1222145558875543</v>
+      </c>
+      <c r="P66" t="n">
+        <v>4687055.047805268</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>418304.8650110241</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2162.96095327205</v>
+      </c>
+      <c r="S66" t="n">
+        <v>98.06439168976064</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1823.828835653621</v>
+      </c>
+      <c r="U66" t="n">
+        <v>83.11285297640444</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>-0.1264 ± 0.1222</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>4687055.0478 ± 418304.8650</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>2162.9610 ± 98.0644</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>1823.8288 ± 83.1129</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.09702150525875733</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>464607.2022428373</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>108.909758026844</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>29.1127865560486</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>-0.04522384586573791</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.02969755150601561</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4292253.001770332</v>
+      </c>
+      <c r="E67" t="n">
+        <v>201312.7535934005</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2071.259558225389</v>
+      </c>
+      <c r="G67" t="n">
+        <v>48.72649553372899</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1855.681256810133</v>
+      </c>
+      <c r="I67" t="n">
+        <v>44.48179755879956</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-0.0452 ± 0.0297</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>4292253.0018 ± 201312.7536</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2071.2596 ± 48.7265</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1855.6813 ± 44.4818</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>-1.585111722634477</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.243080905082388</v>
+      </c>
+      <c r="P67" t="n">
+        <v>10768783.02524476</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>929400.144337276</v>
+      </c>
+      <c r="R67" t="n">
+        <v>3278.85279159589</v>
+      </c>
+      <c r="S67" t="n">
+        <v>141.0571054124456</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2570.118143764929</v>
+      </c>
+      <c r="U67" t="n">
+        <v>172.8449954986473</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>-1.5851 ± 0.2431</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>10768783.0252 ± 929400.1443</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>3278.8528 ± 141.0571</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2570.1181 ± 172.8450</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.539887876768739</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>6476530.02347443</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1207.593233370501</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>714.4368869547955</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>-0.2674879048880762</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.1102508098838784</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5199525.514479999</v>
+      </c>
+      <c r="E68" t="n">
+        <v>418987.0960349165</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2278.580226524359</v>
+      </c>
+      <c r="G68" t="n">
+        <v>91.87954537329404</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1930.904</v>
+      </c>
+      <c r="I68" t="n">
+        <v>87.79568920700689</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-0.2675 ± 0.1103</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>5199525.5145 ± 418987.0960</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2278.5802 ± 91.8795</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1930.9040 ± 87.7957</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>-0.50940040613677</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.2414342496387683</v>
+      </c>
+      <c r="P68" t="n">
+        <v>6260363.105479041</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>802186.6644520612</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2497.471121501854</v>
+      </c>
+      <c r="S68" t="n">
+        <v>159.8648830290949</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2070.284763137528</v>
+      </c>
+      <c r="U68" t="n">
+        <v>120.6611038599134</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>-0.5094 ± 0.2414</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>6260363.1055 ± 802186.6645</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>2497.4711 ± 159.8649</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2070.2848 ± 120.6611</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.2419125012486938</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1060837.590999042</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>218.890894977495</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>139.3807631375284</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.3360615620073734</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.1378329076011162</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5484008.168167765</v>
+      </c>
+      <c r="E69" t="n">
+        <v>576403.3611653862</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2338.817409203663</v>
+      </c>
+      <c r="G69" t="n">
+        <v>124.4601434356985</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1976.35174841514</v>
+      </c>
+      <c r="I69" t="n">
+        <v>123.2861301883126</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-0.3361 ± 0.1378</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>5484008.1682 ± 576403.3612</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2338.8174 ± 124.4601</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1976.3517 ± 123.2861</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>-0.3080616474086598</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.1667474238286133</v>
+      </c>
+      <c r="P69" t="n">
+        <v>5456958.83693452</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>759922.2469249581</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2331.350182220014</v>
+      </c>
+      <c r="S69" t="n">
+        <v>155.5105026722121</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1935.390040832001</v>
+      </c>
+      <c r="U69" t="n">
+        <v>129.4926922363996</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>-0.3081 ± 0.1667</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>5456958.8369 ± 759922.2469</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2331.3502 ± 155.5105</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>1935.3900 ± 129.4927</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.02799991459871354</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-27049.33123324532</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-7.467226983648743</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-40.96170758313906</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>-0.5095897393811551</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.1766848228829434</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6200940.965746299</v>
+      </c>
+      <c r="E70" t="n">
+        <v>777167.7922437319</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2485.674362162478</v>
+      </c>
+      <c r="G70" t="n">
+        <v>157.6350603784267</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2051.180442857143</v>
+      </c>
+      <c r="I70" t="n">
+        <v>176.3899995810382</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-0.5096 ± 0.1767</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>6200940.9657 ± 777167.7922</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2485.6744 ± 157.6351</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2051.1804 ± 176.3900</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>-0.5881716273962396</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.2620870858654061</v>
+      </c>
+      <c r="P70" t="n">
+        <v>6617697.375980625</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1078627.281843615</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2565.256039968876</v>
+      </c>
+      <c r="S70" t="n">
+        <v>203.1934638707781</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2094.319049790908</v>
+      </c>
+      <c r="U70" t="n">
+        <v>146.7954427364796</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>-0.5882 ± 0.2621</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>6617697.3760 ± 1078627.2818</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>2565.2560 ± 203.1935</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2094.3190 ± 146.7954</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.07858188801508448</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>416756.4102343256</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>79.5816778063986</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>43.138606933765</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>-0.9240200916636427</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.2197289926805912</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7901767.635233889</v>
+      </c>
+      <c r="E71" t="n">
+        <v>957048.788964997</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2806.02004944254</v>
+      </c>
+      <c r="G71" t="n">
+        <v>176.4436244885071</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2255.210983333333</v>
+      </c>
+      <c r="I71" t="n">
+        <v>191.7409568707387</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-0.9240 ± 0.2197</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>7901767.6352 ± 957048.7890</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2806.0200 ± 176.4436</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2255.2110 ± 191.7410</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>-0.9207057293678036</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.1346455940171846</v>
+      </c>
+      <c r="P71" t="n">
+        <v>8009991.033006666</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>616382.3816635744</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2828.259395841021</v>
+      </c>
+      <c r="S71" t="n">
+        <v>110.2513433712303</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2273.132322548322</v>
+      </c>
+      <c r="U71" t="n">
+        <v>88.63222868320217</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>-0.9207 ± 0.1346</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>8009991.0330 ± 616382.3817</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>2828.2594 ± 110.2513</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2273.1323 ± 88.6322</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.003314362295839146</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>108223.3977727769</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>22.2393463984813</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>17.92133921498862</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>-0.02197954877106871</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.0931319739814164</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4190833.005087733</v>
+      </c>
+      <c r="E72" t="n">
+        <v>338025.6045214536</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2045.723106278084</v>
+      </c>
+      <c r="G72" t="n">
+        <v>80.62242263014029</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1765.52881925974</v>
+      </c>
+      <c r="I72" t="n">
+        <v>49.61090621555741</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0931</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>4190833.0051 ± 338025.6045</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2045.7231 ± 80.6224</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1765.5288 ± 49.6109</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.006455780373212139</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.04892348421770575</v>
+      </c>
+      <c r="P72" t="n">
+        <v>4146450.483429372</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>304542.6127401009</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2035.049048973221</v>
+      </c>
+      <c r="S72" t="n">
+        <v>74.72803804136105</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1813.932735973819</v>
+      </c>
+      <c r="U72" t="n">
+        <v>87.40337371545974</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0.0065 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>4146450.4834 ± 304542.6127</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>2035.0490 ± 74.7280</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>1813.9327 ± 87.4034</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>-0.02843532914428085</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-44382.52165836096</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-10.67405730486348</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>48.40391671407929</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>-0.02202379141697535</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.09327798340599044</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4191008.940626054</v>
+      </c>
+      <c r="E73" t="n">
+        <v>338623.7087407181</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2045.761228163767</v>
+      </c>
+      <c r="G73" t="n">
+        <v>80.75984953985314</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1765.456276809517</v>
+      </c>
+      <c r="I73" t="n">
+        <v>49.70998560185271</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0933</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>4191008.9406 ± 338623.7087</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2045.7612 ± 80.7598</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1765.4563 ± 49.7100</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0.006443161190610436</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.04891651581300863</v>
+      </c>
+      <c r="P73" t="n">
+        <v>4146501.173366891</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>304493.1542510501</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2035.061920175357</v>
+      </c>
+      <c r="S73" t="n">
+        <v>74.71541874993835</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1813.923255921103</v>
+      </c>
+      <c r="U73" t="n">
+        <v>87.38937488179191</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0.0064 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>4146501.1734 ± 304493.1543</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>2035.0619 ± 74.7154</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>1813.9233 ± 87.3894</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.02846695260758578</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>-44507.76725916285</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-10.69930798840983</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>48.46697911158526</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>-0.02204459551775029</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.09337855142992794</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4191091.420878544</v>
+      </c>
+      <c r="E74" t="n">
+        <v>339054.5694780927</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2045.777829721612</v>
+      </c>
+      <c r="G74" t="n">
+        <v>80.85990833311384</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1765.393478151547</v>
+      </c>
+      <c r="I74" t="n">
+        <v>49.77236918291081</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-0.0220 ± 0.0934</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>4191091.4209 ± 339054.5695</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2045.7778 ± 80.8599</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1765.3935 ± 49.7724</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0.006429976379896229</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.04890982816024889</v>
+      </c>
+      <c r="P74" t="n">
+        <v>4146554.12791614</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>304442.9847094165</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2035.075353304413</v>
+      </c>
+      <c r="S74" t="n">
+        <v>74.70262741964505</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1813.913614388983</v>
+      </c>
+      <c r="U74" t="n">
+        <v>87.37513500768613</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0.0064 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>4146554.1279 ± 304442.9847</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>2035.0754 ± 74.7026</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>1813.9136 ± 87.3751</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.02847457189764652</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>-44537.2929624049</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-10.70247641719948</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>48.52013623743619</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>-0.02363182357272349</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.09562120929438869</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4197301.361197427</v>
+      </c>
+      <c r="E75" t="n">
+        <v>344679.8161882583</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2047.246722126397</v>
+      </c>
+      <c r="G75" t="n">
+        <v>82.20719041373771</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1766.71915181769</v>
+      </c>
+      <c r="I75" t="n">
+        <v>51.57481027024704</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-0.0236 ± 0.0956</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>4197301.3612 ± 344679.8162</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2047.2467 ± 82.2072</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1766.7192 ± 51.5748</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0.006430457294040182</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.04890951231155721</v>
+      </c>
+      <c r="P75" t="n">
+        <v>4146552.212226189</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>304443.5292816404</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2035.074878444234</v>
+      </c>
+      <c r="S75" t="n">
+        <v>74.7027543101815</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1813.913792849644</v>
+      </c>
+      <c r="U75" t="n">
+        <v>87.375358114875</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0.0064 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>4146552.2122 ± 304443.5293</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>2035.0749 ± 74.7028</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>1813.9138 ± 87.3754</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03006228086676367</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-50749.14897123817</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-12.17184368216294</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>47.19464103195423</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>-0.0293523377117139</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.07005792052475614</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4222447.845562431</v>
+      </c>
+      <c r="E76" t="n">
+        <v>248994.8517990398</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2054.051195245206</v>
+      </c>
+      <c r="G76" t="n">
+        <v>60.75024347616055</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1794.716049097572</v>
+      </c>
+      <c r="I76" t="n">
+        <v>61.22856451392724</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-0.0294 ± 0.0701</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>4222447.8456 ± 248994.8518</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2054.0512 ± 60.7502</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1794.7160 ± 61.2286</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>-0.1298772540833849</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.1200854675069694</v>
+      </c>
+      <c r="P76" t="n">
+        <v>4710666.868215402</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>519132.5854161489</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2167.58008441026</v>
+      </c>
+      <c r="S76" t="n">
+        <v>116.7306771228909</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1907.240855702832</v>
+      </c>
+      <c r="U76" t="n">
+        <v>97.28380297497954</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>-0.1299 ± 0.1201</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>4710666.8682 ± 519132.5854</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>2167.5801 ± 116.7307</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>1907.2409 ± 97.2838</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.100524916371671</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>488219.0226529706</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>113.5288891650534</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>112.5248066052598</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>-0.04522384586573791</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.02969755150601561</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4292253.001770332</v>
+      </c>
+      <c r="E77" t="n">
+        <v>201312.7535934005</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2071.259558225389</v>
+      </c>
+      <c r="G77" t="n">
+        <v>48.72649553372899</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1855.681256810133</v>
+      </c>
+      <c r="I77" t="n">
+        <v>44.48179755879956</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-0.0452 ± 0.0297</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>4292253.0018 ± 201312.7536</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2071.2596 ± 48.7265</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1855.6813 ± 44.4818</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>-0.119444220475687</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.05477205586251412</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4673397.506005201</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>365366.9215896982</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2160.340664448072</v>
+      </c>
+      <c r="S77" t="n">
+        <v>83.83661052084295</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1913.191224798294</v>
+      </c>
+      <c r="U77" t="n">
+        <v>96.81010927698871</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>-0.1194 ± 0.0548</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>4673397.5060 ± 365366.9216</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>2160.3407 ± 83.8366</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>1913.1912 ± 96.8101</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.07422037460994904</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>381144.50423487</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>89.0811062226835</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>57.5099679881605</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>-0.2674879048880762</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.1102508098838784</v>
+      </c>
+      <c r="D78" t="n">
+        <v>5199525.514479999</v>
+      </c>
+      <c r="E78" t="n">
+        <v>418987.0960349165</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2278.580226524359</v>
+      </c>
+      <c r="G78" t="n">
+        <v>91.87954537329404</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1930.904</v>
+      </c>
+      <c r="I78" t="n">
+        <v>87.79568920700689</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-0.2675 ± 0.1103</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>5199525.5145 ± 418987.0960</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2278.5802 ± 91.8795</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1930.9040 ± 87.7957</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>-0.2011300080016346</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.06946578729563883</v>
+      </c>
+      <c r="P78" t="n">
+        <v>5009603.737679501</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>344676.7245957914</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2237.038946505775</v>
+      </c>
+      <c r="S78" t="n">
+        <v>76.45252336386987</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1921.600020176245</v>
+      </c>
+      <c r="U78" t="n">
+        <v>75.18441880341632</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>-0.2011 ± 0.0695</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>5009603.7377 ± 344676.7246</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>2237.0389 ± 76.4525</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>1921.6000 ± 75.1844</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>-0.06635789688644153</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>-189921.7768004984</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>-41.54128001858362</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>-9.303979823755071</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>-0.3360615620073734</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1378329076011162</v>
+      </c>
+      <c r="D79" t="n">
+        <v>5484008.168167765</v>
+      </c>
+      <c r="E79" t="n">
+        <v>576403.3611653862</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2338.817409203663</v>
+      </c>
+      <c r="G79" t="n">
+        <v>124.4601434356985</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1976.35174841514</v>
+      </c>
+      <c r="I79" t="n">
+        <v>123.2861301883126</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-0.3361 ± 0.1378</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>5484008.1682 ± 576403.3612</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2338.8174 ± 124.4601</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1976.3517 ± 123.2861</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>-0.1921497592830952</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.1004141674748086</v>
+      </c>
+      <c r="P79" t="n">
+        <v>4977471.6047949</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>526704.1128716948</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2228.375819521219</v>
+      </c>
+      <c r="S79" t="n">
+        <v>114.5659042164179</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1936.371111109163</v>
+      </c>
+      <c r="U79" t="n">
+        <v>104.3496113886036</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>-0.1921 ± 0.1004</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>4977471.6048 ± 526704.1129</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>2228.3758 ± 114.5659</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>1936.3711 ± 104.3496</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>-0.1439118027242782</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>-506536.5633728653</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>-110.4415896824435</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>-39.98063730597733</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>-0.5095897393811551</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.1766848228829434</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6200940.965746299</v>
+      </c>
+      <c r="E80" t="n">
+        <v>777167.7922437319</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2485.674362162478</v>
+      </c>
+      <c r="G80" t="n">
+        <v>157.6350603784267</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2051.180442857143</v>
+      </c>
+      <c r="I80" t="n">
+        <v>176.3899995810382</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-0.5096 ± 0.1767</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>6200940.9657 ± 777167.7922</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2485.6744 ± 157.6351</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2051.1804 ± 176.3900</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>-0.2198215910135217</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.07989282539604484</v>
+      </c>
+      <c r="P80" t="n">
+        <v>5093951.67033181</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>471205.5773051113</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2254.858646985713</v>
+      </c>
+      <c r="S80" t="n">
+        <v>103.0865464094777</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1939.822805199898</v>
+      </c>
+      <c r="U80" t="n">
+        <v>91.86529787293772</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>-0.2198 ± 0.0799</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>5093951.6703 ± 471205.5773</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>2254.8586 ± 103.0865</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>1939.8228 ± 91.8653</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>-0.2897681483676334</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>-1106989.29541449</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>-230.815715176765</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>-111.3576376572446</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>-0.9240200916636427</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.2197289926805912</v>
+      </c>
+      <c r="D81" t="n">
+        <v>7901767.635233889</v>
+      </c>
+      <c r="E81" t="n">
+        <v>957048.788964997</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2806.02004944254</v>
+      </c>
+      <c r="G81" t="n">
+        <v>176.4436244885071</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2255.210983333333</v>
+      </c>
+      <c r="I81" t="n">
+        <v>191.7409568707387</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-0.9240 ± 0.2197</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>7901767.6352 ± 957048.7890</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2806.0200 ± 176.4436</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2255.2110 ± 191.7410</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>-0.7328266672368908</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.1755664423745648</v>
+      </c>
+      <c r="P81" t="n">
+        <v>7224309.491849869</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>769090.78526603</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2684.481332654806</v>
+      </c>
+      <c r="S81" t="n">
+        <v>140.9076390869193</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2209.68196979916</v>
+      </c>
+      <c r="U81" t="n">
+        <v>124.9356439375182</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>-0.7328 ± 0.1756</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>7224309.4918 ± 769090.7853</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>2684.4813 ± 140.9076</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2209.6820 ± 124.9356</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>-0.1911934244267519</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>-677458.1433840198</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>-121.5387167877334</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>-45.52901353417337</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -9306,31 +14162,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
@@ -9448,6 +14304,44 @@
       </c>
       <c r="E7" t="n">
         <v>1003.830611824549</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.06319251159397618</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-179571.8982935199</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-34.59749916704243</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.64491793673249</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4712938991565455</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2034483.562385267</v>
+      </c>
+      <c r="D9" t="n">
+        <v>413.3563253453579</v>
+      </c>
+      <c r="E9" t="n">
+        <v>292.0914715509197</v>
       </c>
     </row>
   </sheetData>
@@ -9465,152 +14359,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -10751,152 +15645,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -12037,152 +16931,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -13323,152 +18217,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -14609,152 +19503,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
